--- a/output/pdf_financials_xlsx/TECK.B.xlsx
+++ b/output/pdf_financials_xlsx/TECK.B.xlsx
@@ -2212,13 +2212,13 @@
         <v>141</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>585</v>
+        <v>2775</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>461</v>
+        <v>2389</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>523</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="49">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/output/pdf_financials_xlsx/TECK.B.xlsx
+++ b/output/pdf_financials_xlsx/TECK.B.xlsx
@@ -1176,10 +1176,10 @@
         <v>1010</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2308</v>
+        <v>-312</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>283</v>
+        <v>-923</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>1072</v>
@@ -2524,31 +2524,31 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>24673</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>28079</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>28503</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>30156</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>32951</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>37095</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>68889</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>44028</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>44391</v>
       </c>
     </row>
     <row r="57">
@@ -2563,31 +2563,31 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>764</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>5512</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>6194</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>7012</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>8014</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>9284</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>23324</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>13460</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>14670</v>
       </c>
     </row>
     <row r="58">
@@ -4303,13 +4303,13 @@
         <v>1010</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>2308</v>
+        <v>-312</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>283</v>
+        <v>-923</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>1072</v>
+        <v>-1072</v>
       </c>
     </row>
     <row r="100">
@@ -7136,7 +7136,11 @@
           <t>Lease liabilities (Note 21(c))</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -15546,7 +15550,11 @@
           <t>Profit (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -15591,7 +15599,7 @@
         <v>-923</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>1072</v>
+        <v>-1072</v>
       </c>
     </row>
     <row r="152">
@@ -18068,7 +18076,11 @@
           <t>Loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -25132,7 +25144,11 @@
           <t>Share of profit of joint venture (Note 16)</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -25324,7 +25340,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -25584,7 +25604,11 @@
           <t>Loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
